--- a/public/converted/prihod-maunfild-03-10-26.xlsx
+++ b/public/converted/prihod-maunfild-03-10-26.xlsx
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD THAMES 601PM белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD THAMES 601PM белый б/у</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower 50 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower 50 черный б/у</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,7 +487,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower A 60 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower A 60 черный б/у</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby 850LED нержавеющая сталь (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby 850LED нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -519,7 +519,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Touch 850 60 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Touch 850 60 черный б/у</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -535,7 +535,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Singl 5028 нержавеющая сталь (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Singl 5028 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Power 50 нержавеющая сталь (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Power 50 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -567,7 +567,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.43.33CB\G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.43.33CB\G б/у</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -583,7 +583,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHS.64.73CS/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHS.64.73CS/G б/у</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -599,7 +599,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.64.43CW/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.64.43CW/G б/у</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -615,7 +615,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594SB2BKF Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594SB2BKF Inverter б/у</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -631,7 +631,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.64.6CW/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.64.6CW/G б/у</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -647,7 +647,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Микроволновая печь встраиваемая MAUNFELD JBMO.20.5GRIB (Китай)</t>
+          <t>Микроволновая печь встраиваемая MAUNFELD JBMO.20.5GRIB б/у</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -663,7 +663,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Электрическая варочная панель MAUNFELD CVCE774SMTBK (Китай)</t>
+          <t>Электрическая варочная панель MAUNFELD CVCE774SMTBK б/у</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -679,7 +679,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Электрическая варочная панель MAUNFELD CVCE292SDBK (Китай)</t>
+          <t>Электрическая варочная панель MAUNFELD CVCE292SDBK б/у</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -695,7 +695,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Мультиварка MAUNFELD MPMC-1624S (Китай)</t>
+          <t>Мультиварка MAUNFELD MPMC-1624S б/у</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -711,7 +711,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Мультиварка MAUNFELD MPMC-1625S (Китай)</t>
+          <t>Мультиварка MAUNFELD MPMC-1625S б/у</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -727,7 +727,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Мясорубка MAUNFELD MF-221SS (Китай)</t>
+          <t>Мясорубка MAUNFELD MF-221SS б/у</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -743,7 +743,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.43.3STS-EW (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.43.3STS-EW б/у</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.32.73CB2/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.32.73CB2/G б/у</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -775,7 +775,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.32.6CB/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.32.6CB/G б/у</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -791,7 +791,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594SF2MDGR LUX Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594SF2MDGR LUX Inverter б/у</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -807,7 +807,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD AVI594BK (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD AVI594BK б/у</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -823,7 +823,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI453STBKC (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI453STBKC б/у</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -839,7 +839,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594SF2WHD Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594SF2WHD Inverter б/у</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -855,7 +855,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Электрическая варочная панель MAUNFELD CVCE594STBK (Китай)</t>
+          <t>Электрическая варочная панель MAUNFELD CVCE594STBK б/у</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -871,7 +871,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Электрическая варочная панель MAUNFELD CVCE594BDBK (Китай)</t>
+          <t>Электрическая варочная панель MAUNFELD CVCE594BDBK б/у</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -887,7 +887,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Паровая швабра MAUNFELD MF-1937BL PRO (Китай)</t>
+          <t>Паровая швабра MAUNFELD MF-1937BL PRO б/у</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -903,7 +903,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Паровая швабра MAUNFELD MF-1938GR (Китай)</t>
+          <t>Паровая швабра MAUNFELD MF-1938GR б/у</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -919,7 +919,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный беспроводной MAUNFELD MF-2034OR PRO (Китай)</t>
+          <t>Пылесос вертикальный беспроводной MAUNFELD MF-2034OR PRO б/у</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -935,7 +935,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Микроволновая печь MAUNFELD MFSMO.20.7 SGW  (Китай)</t>
+          <t>Микроволновая печь MAUNFELD MFSMO.20.7 SGW б/у</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -951,7 +951,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Light 60 нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Light 60 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -967,7 +967,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Light 5028 чёрный (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Light 5028 чёрный б/у</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -983,7 +983,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Cork 60 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Cork 60 черный б/у</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -999,7 +999,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Light C 60 нержавеющая сталь (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Light C 60 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1015,7 +1015,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 белый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 белый б/у</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1031,7 +1031,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602M нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602M нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1047,7 +1047,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Power 50 черный (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Power 50 черный б/у</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1063,7 +1063,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.32.1CB/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.32.1CB/G б/у</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1079,7 +1079,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Микроволновая печь MAUNFELD JFSMO.20.5.GRBG (Китай)</t>
+          <t>Микроволновая печь MAUNFELD JFSMO.20.5.GRBG б/у</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1095,7 +1095,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI453WH (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI453WH б/у</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1111,7 +1111,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.43.23CW\G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.43.23CW\G б/у</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1127,7 +1127,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594BG (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594BG б/у</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1143,7 +1143,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.64.6CW/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.64.6CW/G б/у</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1159,7 +1159,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.64.23CB\G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.64.23CB\G б/у</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1175,7 +1175,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594SBG Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594SBG Inverter б/у</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1191,7 +1191,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594SF2BK Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594SF2BK Inverter б/у</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1207,7 +1207,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Холодильник MAUNFELD MFF83B (Китай)</t>
+          <t>Холодильник MAUNFELD MFF83B б/у</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1223,7 +1223,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI604SBEXWH Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI604SBEXWH Inverter б/у</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1239,7 +1239,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD AVI6044SSFBK (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD AVI6044SSFBK б/у</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1255,7 +1255,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-635DBR (Китай)</t>
+          <t>Чайник MAUNFELD MGK-635DBR б/у</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1271,7 +1271,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10THGBG (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10THGBG б/у</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1287,7 +1287,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-625BL (Китай)</t>
+          <t>Чайник MAUNFELD MGK-625BL б/у</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1303,7 +1303,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-625S (Китай)</t>
+          <t>Чайник MAUNFELD MGK-625S б/у</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1319,7 +1319,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10TGB (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10TGB б/у</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1335,7 +1335,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK6709S (Китай)</t>
+          <t>Чайник MAUNFELD MGK6709S б/у</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1351,7 +1351,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Вафельница MAUNFELD MF-1431BL (Китай)</t>
+          <t>Вафельница MAUNFELD MF-1431BL б/у</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1367,7 +1367,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-631B (Китай)</t>
+          <t>Чайник MAUNFELD MGK-631B б/у</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1383,7 +1383,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-616DBK (Китай)</t>
+          <t>Чайник MAUNFELD MGK-616DBK б/у</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1399,7 +1399,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-635DBK (Китай)</t>
+          <t>Чайник MAUNFELD MGK-635DBK б/у</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1415,7 +1415,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK6710S (Китай)</t>
+          <t>Чайник MAUNFELD MGK6710S б/у</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1431,7 +1431,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Электрическая плитка MAUNFELD SEHE.231W (Китай)</t>
+          <t>Электрическая плитка MAUNFELD SEHE.231W б/у</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1447,7 +1447,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MFT-847BK (Китай)</t>
+          <t>Тостер MAUNFELD MFT-847BK б/у</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1463,7 +1463,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Электрическая плитка MAUNFELD SEHE.231B (Китай)</t>
+          <t>Электрическая плитка MAUNFELD SEHE.231B б/у</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1479,7 +1479,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFB10GGR (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFB10GGR б/у</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1495,7 +1495,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD GERDA MCS44S07 из нержавеющей стали со стеклянной крышкой, 22 см, 4,4 л. (Китай)</t>
+          <t>Кастрюля MAUNFELD GERDA MCS44S07 из нержавеющей стали со стеклянной крышкой, 22 см, 4,4 л. б/у</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1511,7 +1511,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFB08GW (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFB08GW б/у</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1527,7 +1527,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-635DGN (Китай)</t>
+          <t>Чайник MAUNFELD MGK-635DGN б/у</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1543,7 +1543,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK1710GW (Китай)</t>
+          <t>Чайник MAUNFELD MGK1710GW б/у</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1559,7 +1559,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-625BG (Китай)</t>
+          <t>Чайник MAUNFELD MGK-625BG б/у</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1575,7 +1575,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821BZ (Китай)</t>
+          <t>Тостер MAUNFELD MF-821BZ б/у</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1591,7 +1591,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE12GB (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE12GB б/у</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1607,7 +1607,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-635DBG (Китай)</t>
+          <t>Чайник MAUNFELD MGK-635DBG б/у</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1623,7 +1623,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD LAURA MCS56S08GR из нержавеющей стали со стеклянной крышкой, 24 см, 5,6. (Китай)</t>
+          <t>Кастрюля MAUNFELD LAURA MCS56S08GR из нержавеющей стали со стеклянной крышкой, 24 см, 5,6. б/у</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1639,7 +1639,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Мясорубка MAUNFELD MF-233BK (Китай)</t>
+          <t>Мясорубка MAUNFELD MF-233BK б/у</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1655,7 +1655,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Электрическая плитка MAUNFELD SEHE.232B (Китай)</t>
+          <t>Электрическая плитка MAUNFELD SEHE.232B б/у</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1671,7 +1671,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10THGW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10THGW б/у</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1687,7 +1687,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MFK-631CH (Китай)</t>
+          <t>Чайник MAUNFELD MFK-631CH б/у</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1703,7 +1703,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-635DGR (Китай)</t>
+          <t>Чайник MAUNFELD MGK-635DGR б/у</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1719,7 +1719,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Мясорубка MAUNFELD MMG.231W (Китай)</t>
+          <t>Мясорубка MAUNFELD MMG.231W б/у</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1735,7 +1735,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-632W (Китай)</t>
+          <t>Чайник MAUNFELD MGK-632W б/у</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1751,7 +1751,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Блендер MAUNFELD MHBL.1000S (Китай)</t>
+          <t>Блендер MAUNFELD MHBL.1000S б/у</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1767,7 +1767,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Power 50 белый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Power 50 белый б/у</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1783,7 +1783,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Light 60 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Light 60 белый б/у</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1799,7 +1799,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 бежевый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 бежевый б/у</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1815,7 +1815,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD THAMES 601M нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD THAMES 601M нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1831,7 +1831,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602M белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602M белый б/у</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1847,7 +1847,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Отпариватель MAUNFELD MF-1138GR PRO (Китай)</t>
+          <t>Отпариватель MAUNFELD MF-1138GR PRO б/у</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1863,7 +1863,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Микроволновая печь MAUNFELD JFSMO.20.5.GRIB (Китай)</t>
+          <t>Микроволновая печь MAUNFELD JFSMO.20.5.GRIB б/у</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1879,7 +1879,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Medway 60 белый\вставка сатин (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Medway 60 белый\вставка сатин б/у</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1895,7 +1895,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602M черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602M черный б/у</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1911,7 +1911,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Мультиварка MAUNFELD MF-1621BR (Китай)</t>
+          <t>Мультиварка MAUNFELD MF-1621BR б/у</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1927,7 +1927,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Кофеварка MAUNFELD MF-737BG PRO (Китай)</t>
+          <t>Кофеварка MAUNFELD MF-737BG PRO б/у</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1943,7 +1943,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Микроволновая печь MAUNFELD MFSMO.20.7WH (Китай)</t>
+          <t>Микроволновая печь MAUNFELD MFSMO.20.7WH б/у</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1959,7 +1959,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594SWH (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594SWH б/у</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1975,7 +1975,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594SB2BKA Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594SB2BKA Inverter б/у</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1991,7 +1991,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Холодильник MAUNFELD MFF83W (Китай)</t>
+          <t>Холодильник MAUNFELD MFF83W б/у</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2007,7 +2007,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Aurora 90 черный матовый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Aurora 90 черный матовый б/у</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2023,7 +2023,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD THAMES 601M белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD THAMES 601M белый б/у</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2039,7 +2039,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Hardy 60 черный (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Hardy 60 черный б/у</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2055,7 +2055,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 601GG черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 601GG черный б/у</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2071,7 +2071,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI292S2BBK Inverter Х</t>
+          <t>Индукционная варочная панель MAUNFELD CVI292S2BBK Inverter Х б/у</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2087,7 +2087,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 601GG белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 601GG белый б/у</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2103,7 +2103,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Электрическая варочная панель MAUNFELD CVCE292MBK2 (Китай)</t>
+          <t>Электрическая варочная панель MAUNFELD CVCE292MBK2 б/у</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2119,7 +2119,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Электрическая варочная панель MAUNFELD EVCE.292-BK (Китай)</t>
+          <t>Электрическая варочная панель MAUNFELD EVCE.292-BK б/у</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2135,7 +2135,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower 90 чёрный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower 90 чёрный б/у</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2151,7 +2151,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 черный (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 черный б/у</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2167,7 +2167,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFE10GB (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFE10GB б/у</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2183,7 +2183,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFB10GB (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFB10GB б/у</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2199,7 +2199,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ковш из литого алюминия со стеклянной крышкой, 18 см, 1,6 л MAUNFELD GRETA MF18GRTT01SP (РОССИЯ)</t>
+          <t>Ковш из литого алюминия со стеклянной крышкой, 18 см, 1,6 л MAUNFELD GRETA MF18GRTT01SP б/у</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2215,7 +2215,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Мясорубка MAUNFELD MMG.2000BRSV (Китай)</t>
+          <t>Мясорубка MAUNFELD MMG.2000BRSV б/у</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2231,7 +2231,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI292S2BBKF Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI292S2BBKF Inverter б/у</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2247,7 +2247,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Кастрюля из литого алюминия со стеклянной крышкой, 24 см, 4 л MAUNFELD GRETA MF24GRTT01CR (Россия)</t>
+          <t>Кастрюля из литого алюминия со стеклянной крышкой, 24 см, 4 л MAUNFELD GRETA MF24GRTT01CR б/у</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2263,7 +2263,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD AVI3027SBK (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD AVI3027SBK б/у</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2279,7 +2279,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Гриль электрический MAUNFELD MF-1311B (Китай)</t>
+          <t>Гриль электрический MAUNFELD MF-1311B б/у</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2295,7 +2295,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Паровая швабра MAUNFELD MF-1936BL (Китай)</t>
+          <t>Паровая швабра MAUNFELD MF-1936BL б/у</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2311,7 +2311,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-612BK (Китай)</t>
+          <t>Чайник MAUNFELD MGK-612BK б/у</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2327,7 +2327,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD CARMEL MF22CRM01CR из литого алюминия со стеклянной крышкой, 22 см, 3 л (Россия)</t>
+          <t>Кастрюля MAUNFELD CARMEL MF22CRM01CR из литого алюминия со стеклянной крышкой, 22 см, 3 л б/у</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2343,7 +2343,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821BL (Китай)</t>
+          <t>Тостер MAUNFELD MF-821BL б/у</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2359,7 +2359,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Мясорубка MAUNFELD MMG.2000W (Китай)</t>
+          <t>Мясорубка MAUNFELD MMG.2000W б/у</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2375,7 +2375,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 нержавеющая сталь (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Singl 60 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2391,7 +2391,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.64.63CBG/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.64.63CBG/G б/у</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2407,7 +2407,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Touch 850 60 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Touch 850 60 белый б/у</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2423,7 +2423,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Кофеварка MAUNFELD MF-723S (Китай)</t>
+          <t>Кофеварка MAUNFELD MF-723S б/у</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2439,7 +2439,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD EVI.292-WH (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD EVI.292-WH б/у</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2455,7 +2455,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AEOH60102S (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AEOH60102S б/у</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2471,7 +2471,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD CARMEL MF24CRM01FP из литого алюминия, 24 см (Россия)</t>
+          <t>Сковорода MAUNFELD CARMEL MF24CRM01FP из литого алюминия, 24 см б/у</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2487,7 +2487,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI292S2BWH Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI292S2BWH Inverter б/у</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2503,7 +2503,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Cork 60 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Cork 60 белый б/у</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2519,7 +2519,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Мясорубка MAUNFELD MF-233WH (Китай)</t>
+          <t>Мясорубка MAUNFELD MF-233WH б/у</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2535,7 +2535,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.32.1CW/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.32.1CW/G б/у</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2551,7 +2551,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD THAMES 601M черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD THAMES 601M черный б/у</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2567,7 +2567,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Singl 5028 бежевый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Singl 5028 бежевый б/у</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2583,7 +2583,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AMCO537GW (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AMCO537GW б/у</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2599,7 +2599,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический с СВЧ MAUNFELD MEOR7217SMB (Китай)</t>
+          <t>Шкаф духовой электрический с СВЧ MAUNFELD MEOR7217SMB б/у</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2615,7 +2615,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AEOD60103B2 (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AEOD60103B2 б/у</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2631,7 +2631,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AEOF6060B2 (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AEOF6060B2 б/у</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2647,7 +2647,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AEOH6066B (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AEOH6066B б/у</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -2663,7 +2663,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AEOH60106S (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AEOH60106S б/у</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -2679,7 +2679,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VSQ 60 нержавеющая сталь/белое стекло (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VSQ 60 нержавеющая сталь/белое стекло б/у</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -2695,7 +2695,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602IG черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602IG черный б/у</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -2711,7 +2711,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Кухонный комбайн 3в1 MAUNFELD MF-433CH PRO (Китай)</t>
+          <t>Кухонный комбайн 3в1 MAUNFELD MF-433CH PRO б/у</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -2727,7 +2727,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Микроволновая печь MAUNFELD MFSMO720EW02 (Китай)</t>
+          <t>Микроволновая печь MAUNFELD MFSMO720EW02 б/у</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -2743,7 +2743,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Fast 60 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Fast 60 белый б/у</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -2759,7 +2759,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Light Glass 60 белое стекло (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Light Glass 60 белое стекло б/у</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -2775,7 +2775,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Light 50 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Light 50 черный б/у</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -2791,7 +2791,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Light 50 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Light 50 белый б/у</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -2807,7 +2807,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Power 60 нержавеющая сталь (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Power 60 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -2823,7 +2823,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Aurora 60 черный матовый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Aurora 60 черный матовый б/у</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -2839,7 +2839,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.64.6CB/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.64.6CB/G б/у</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -2855,7 +2855,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594BK (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594BK б/у</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -2871,7 +2871,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10THGGR (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10THGGR б/у</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -2887,7 +2887,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10TGGR (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10TGGR б/у</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -2903,7 +2903,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE12GGR (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE12GGR б/у</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -2919,7 +2919,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ручной отпариватель MAUNFELD MF-1134GR (Китай)</t>
+          <t>Ручной отпариватель MAUNFELD MF-1134GR б/у</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -2935,7 +2935,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFE10THGB (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFE10THGB б/у</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -2951,7 +2951,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Проточный электрический водонагреватель MAUNFELD MWH55IS (Китай)</t>
+          <t>Проточный электрический водонагреватель MAUNFELD MWH55IS б/у</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -2967,7 +2967,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK1710GS (Китай)</t>
+          <t>Чайник MAUNFELD MGK1710GS б/у</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -2983,7 +2983,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ручной отпариватель MAUNFELD MF-1132GR (Китай)</t>
+          <t>Ручной отпариватель MAUNFELD MF-1132GR б/у</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2999,7 +2999,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX10BG (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX10BG б/у</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -3015,7 +3015,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFS12TW (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFS12TW б/у</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3031,7 +3031,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Блендер MAUNFELD MF-132W (Китай)</t>
+          <t>Блендер MAUNFELD MF-132W б/у</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -3047,7 +3047,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10TGBG (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10TGBG б/у</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3063,7 +3063,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFB12GBG (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFB12GBG б/у</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -3079,7 +3079,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MFK-624B (Китай)</t>
+          <t>Чайник MAUNFELD MFK-624B б/у</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -3095,7 +3095,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX10TW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX10TW б/у</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -3111,7 +3111,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Кофемолка MAUNFELD MF-523S (Китай)</t>
+          <t>Кофемолка MAUNFELD MF-523S б/у</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3127,7 +3127,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Вафельница MAUNFELD MF-1436WH (Китай)</t>
+          <t>Вафельница MAUNFELD MF-1436WH б/у</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -3143,7 +3143,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Паровая швабра MAUNFELD MF-1932W (Китай)</t>
+          <t>Паровая швабра MAUNFELD MF-1932W б/у</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3159,7 +3159,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Паровая швабра MAUNFELD MF-1933BL PRO (Китай)</t>
+          <t>Паровая швабра MAUNFELD MF-1933BL PRO б/у</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -3175,7 +3175,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Паровая швабра MAUNFELD MF-1934GR (Китай)</t>
+          <t>Паровая швабра MAUNFELD MF-1934GR б/у</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3191,7 +3191,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Кофемашина рожкового типа MAUNFELD MF-720S PRO (Китай)</t>
+          <t>Кофемашина рожкового типа MAUNFELD MF-720S PRO б/у</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3207,7 +3207,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Миксер планетарный MAUNFELD MF-431CH (Китай)</t>
+          <t>Миксер планетарный MAUNFELD MF-431CH б/у</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3223,7 +3223,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Блендер MAUNFELD MBL.1000S (Китай)</t>
+          <t>Блендер MAUNFELD MBL.1000S б/у</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3239,7 +3239,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Паровая швабра MAUNFELD MF-1935R (Китай)</t>
+          <t>Паровая швабра MAUNFELD MF-1935R б/у</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3255,7 +3255,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Блендер MAUNFELD MF-121S (Китай)</t>
+          <t>Блендер MAUNFELD MF-121S б/у</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3271,7 +3271,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TS Touch 50 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TS Touch 50 белый б/у</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3287,7 +3287,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD FRIDA MCS47FA02DG из кованого алюминия со стеклянной крышкой, 24 см, 4,7 л. (Китай)</t>
+          <t>Кастрюля MAUNFELD FRIDA MCS47FA02DG из кованого алюминия со стеклянной крышкой, 24 см, 4,7 л. б/у</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3303,7 +3303,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD LAURA MCS22S08GR из нержавеющей стали со стеклянной крышкой, 18 см, 2,2 л. (Китай)</t>
+          <t>Кастрюля MAUNFELD LAURA MCS22S08GR из нержавеющей стали со стеклянной крышкой, 18 см, 2,2 л. б/у</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3319,7 +3319,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD CARMEL MF26CRM01CR из литого алюминия со стеклянной крышкой, 26 см, 5 л (Россия)</t>
+          <t>Кастрюля MAUNFELD CARMEL MF26CRM01CR из литого алюминия со стеклянной крышкой, 26 см, 5 л б/у</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3335,7 +3335,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Электрическая плитка MAUNFELD SEHE.232W (Китай)</t>
+          <t>Электрическая плитка MAUNFELD SEHE.232W б/у</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3351,7 +3351,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.64.63CB.R/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.64.63CB.R/G б/у</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3367,7 +3367,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Глубокая сковорода MAUNFELD HOWARD MDP30LCL15 из облегченного чугуна со стеклянной крышкой, 30 см (Китай)</t>
+          <t>Глубокая сковорода MAUNFELD HOWARD MDP30LCL15 из облегченного чугуна со стеклянной крышкой, 30 см б/у</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3383,7 +3383,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.64.2CW\G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.64.2CW\G б/у</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3399,7 +3399,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD EVI.594ST-BK (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD EVI.594ST-BK б/у</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3415,7 +3415,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.43.33CW\G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.43.33CW\G б/у</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3431,7 +3431,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Электрическая варочная панель MAUNFELD AVCE453BK (Китай)</t>
+          <t>Электрическая варочная панель MAUNFELD AVCE453BK б/у</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3447,7 +3447,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD FRIDA MCS29FA02DG из кованого алюминия со стеклянной крышкой, 20 см, 2,9 л (Китай)</t>
+          <t>Кастрюля MAUNFELD FRIDA MCS29FA02DG из кованого алюминия со стеклянной крышкой, 20 см, 2,9 л б/у</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3463,7 +3463,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Мультиварка MAUNFELD MF-1623WH (Китай)</t>
+          <t>Мультиварка MAUNFELD MF-1623WH б/у</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3479,7 +3479,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD LAURA MCS40S08GR из нержавеющей стали со стеклянной крышкой, 22 см, 4 л. (Китай)</t>
+          <t>Кастрюля MAUNFELD LAURA MCS40S08GR из нержавеющей стали со стеклянной крышкой, 22 см, 4 л. б/у</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3495,7 +3495,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Кофемашина рожкового типа MAUNFELD MF-733BK (Китай)</t>
+          <t>Кофемашина рожкового типа MAUNFELD MF-733BK б/у</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3511,7 +3511,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Кастрюля FILIGRANA STELLA FG50STL01CR  из нержавеющей стали со стеклянной крышкой, 22  см, 4,7 л.</t>
+          <t>Кастрюля FILIGRANA STELLA FG50STL01CR  из нержавеющей стали со стеклянной крышкой, 22  см, 4,7 л. б/у</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3527,7 +3527,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Мясорубка MAUNFELD MF-232WG (Китай)</t>
+          <t>Мясорубка MAUNFELD MF-232WG б/у</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -3543,7 +3543,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10GW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10GW б/у</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -3559,7 +3559,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE12GBG (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE12GBG б/у</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3575,7 +3575,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE12TGW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE12TGW б/у</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3591,7 +3591,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MFK-631DB (Китай)</t>
+          <t>Чайник MAUNFELD MFK-631DB б/у</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3607,7 +3607,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MFK-6111G (Китай)</t>
+          <t>Чайник MAUNFELD MFK-6111G б/у</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3623,7 +3623,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFB12GGR (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFB12GGR б/у</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -3639,7 +3639,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFS12TS (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFS12TS б/у</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -3655,7 +3655,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX12S (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX12S б/у</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -3671,7 +3671,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-626BK (Китай)</t>
+          <t>Чайник MAUNFELD MGK-626BK б/у</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -3687,7 +3687,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Миксер планетарный MAUNFELD MF-431BK (Китай)</t>
+          <t>Миксер планетарный MAUNFELD MF-431BK б/у</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3703,7 +3703,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821MINT (Китай)</t>
+          <t>Тостер MAUNFELD MF-821MINT б/у</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -3719,7 +3719,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Ковш MAUNFELD HELGA MSP14FA05FS из кованого алюминия со стеклянной крышкой, 16 см, 1,4 л. (Китай)</t>
+          <t>Ковш MAUNFELD HELGA MSP14FA05FS из кованого алюминия со стеклянной крышкой, 16 см, 1,4 л. б/у</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -3735,7 +3735,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK-633BK (Китай)</t>
+          <t>Чайник MAUNFELD MGK-633BK б/у</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -3751,7 +3751,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821BG (Китай)</t>
+          <t>Тостер MAUNFELD MF-821BG б/у</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -3767,7 +3767,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX12BG (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX12BG б/у</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -3783,7 +3783,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Канальный вентилятор MAUNFELD MFDL10W (Китай)</t>
+          <t>Канальный вентилятор MAUNFELD MFDL10W б/у</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -3799,7 +3799,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Миксер MAUNFELD MF-331BL (Китай)</t>
+          <t>Миксер MAUNFELD MF-331BL б/у</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -3815,7 +3815,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Блендер MAUNFELD MF-122S (Китай)</t>
+          <t>Блендер MAUNFELD MF-122S б/у</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3831,7 +3831,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10GGR (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10GGR б/у</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -3847,7 +3847,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MGK6702B (Китай)</t>
+          <t>Чайник MAUNFELD MGK6702B б/у</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -3863,7 +3863,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD HELGA MCS57FA05FS из кованого алюминия со стеклянной крышкой, 24 см, 5,7 л. (Китай)</t>
+          <t>Кастрюля MAUNFELD HELGA MCS57FA05FS из кованого алюминия со стеклянной крышкой, 24 см, 5,7 л. б/у</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -3879,7 +3879,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD ASTRID MF24ASTR1CR из кованого алюминия со стеклянной крышкой, 24см, 4.6 л (Китай)</t>
+          <t>Кастрюля MAUNFELD ASTRID MF24ASTR1CR из кованого алюминия со стеклянной крышкой, 24см, 4.6 л б/у</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -3895,7 +3895,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821S (Китай)</t>
+          <t>Тостер MAUNFELD MF-821S б/у</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -3911,7 +3911,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Миксер MAUNFELD MF-331R (Китай)</t>
+          <t>Миксер MAUNFELD MF-331R б/у</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -3927,7 +3927,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Light 60 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Light 60 черный б/у</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -3943,7 +3943,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower 60 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower 60 черный б/у</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -3959,7 +3959,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.32.3EW\G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.32.3EW\G б/у</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -3975,7 +3975,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Холодильник MAUNFELD MFF50WD (Китай)</t>
+          <t>Холодильник MAUNFELD MFF50WD б/у</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3991,7 +3991,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Холодильник MAUNFELD MFF83SL (Китай)</t>
+          <t>Холодильник MAUNFELD MFF83SL б/у</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -4007,7 +4007,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI453SBWH Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI453SBWH Inverter б/у</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -4023,7 +4023,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI453SBBK LUX Inverter (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI453SBBK LUX Inverter б/у</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -4039,7 +4039,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD THAMES 601PM черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD THAMES 601PM черный б/у</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -4055,7 +4055,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD THAMES 601PM нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD THAMES 601PM нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -4071,7 +4071,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.32.63CB/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.32.63CB/G б/у</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -4087,7 +4087,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель HOMSair HI32ABK (Китай)</t>
+          <t>Индукционная варочная панель HOMSair HI32ABK б/у</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -4103,7 +4103,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.64.63CB2/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.64.63CB2/G б/у</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -4119,7 +4119,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Fast 60 нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Fast 60 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -4135,7 +4135,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower 50 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower 50 белый б/у</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -4151,7 +4151,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower 60 белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower 60 белый б/у</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -4167,7 +4167,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Wind 60 A черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Wind 60 A черный б/у</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -4183,7 +4183,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Холодильник MAUNFELD MFF83WD (Китай)</t>
+          <t>Холодильник MAUNFELD MFF83WD б/у</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -4199,7 +4199,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Fast Glass 60 бежевый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Fast Glass 60 бежевый б/у</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -4215,7 +4215,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower A 60 белый(Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower A 60 белый б/у</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -4231,7 +4231,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Wind 60 A белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Wind 60 A белый б/у</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -4247,7 +4247,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD THAMES 603PM белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD THAMES 603PM белый б/у</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4263,7 +4263,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Fast 60 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Fast 60 черный б/у</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -4279,7 +4279,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD VS Light 50 нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD VS Light 50 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -4295,7 +4295,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Холодильник MAUNFELD MFF83RR (Китай)</t>
+          <t>Холодильник MAUNFELD MFF83RR б/у</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -4311,7 +4311,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Astro 50 белое стекло (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Astro 50 белое стекло б/у</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -4327,7 +4327,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 603EM нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 603EM нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -4343,7 +4343,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI594MBGBR (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI594MBGBR б/у</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -4359,7 +4359,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHG.64.63CW/G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHG.64.63CW/G б/у</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -4375,7 +4375,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Газовая варочная панель MAUNFELD EGHE.75.33CW\G (Турция)</t>
+          <t>Газовая варочная панель MAUNFELD EGHE.75.33CW\G б/у</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -4391,7 +4391,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Hardy 60 белый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Hardy 60 белый б/у</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -4407,7 +4407,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Flat 52 нержавеющая сталь (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Flat 52 нержавеющая сталь б/у</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -4423,7 +4423,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Rocky 60 белый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Rocky 60 белый б/у</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -4439,7 +4439,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602IG белый (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD TRAPEZE 602IG белый б/у</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -4455,7 +4455,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower A 50 черный (Китай)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower A 50 черный б/у</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -4471,7 +4471,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Индукционная варочная панель MAUNFELD CVI292BG (Китай)</t>
+          <t>Индукционная варочная панель MAUNFELD CVI292BG б/у</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -4487,7 +4487,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFS10TW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFS10TW б/у</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -4503,7 +4503,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MFK-647BK (Китай)</t>
+          <t>Чайник MAUNFELD MFK-647BK б/у</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -4519,7 +4519,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MFK-624BZ (Китай)</t>
+          <t>Чайник MAUNFELD MFK-624BZ б/у</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -4535,7 +4535,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Кастрюля MAUNFELD MARTA MCS41FA06CL из кованого алюминия со стеклянной крышкой, 24 см, 4,1 л. (Китай)</t>
+          <t>Кастрюля MAUNFELD MARTA MCS41FA06CL из кованого алюминия со стеклянной крышкой, 24 см, 4,1 л. б/у</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -4551,7 +4551,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD DEVON MFP20CE16R из эмалированного чугуна, 20 см (Китай)</t>
+          <t>Сковорода MAUNFELD DEVON MFP20CE16R из эмалированного чугуна, 20 см б/у</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -4567,7 +4567,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD DEVON MFP24CE16R из эмалированного чугуна, 24 см (Китай)</t>
+          <t>Сковорода MAUNFELD DEVON MFP24CE16R из эмалированного чугуна, 24 см б/у</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -4583,7 +4583,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD HELGA MFP20FA05FS из кованого алюминия, 20 см (Китай)</t>
+          <t>Сковорода MAUNFELD HELGA MFP20FA05FS из кованого алюминия, 20 см б/у</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -4599,7 +4599,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Сковорода из литого алюминия, 26 см MAUNFELD ALVA MF26LV01FP (РОССИЯ)</t>
+          <t>Сковорода из литого алюминия, 26 см MAUNFELD ALVA MF26LV01FP б/у</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -4615,7 +4615,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD FRIDA MFP28FA02DG из кованого алюминия, 28 см (Китай)</t>
+          <t>Сковорода MAUNFELD FRIDA MFP28FA02DG из кованого алюминия, 28 см б/у</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -4631,7 +4631,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Сковорода глубокая FILIGRANA EDDA FG26EDD01DF из кованого алюминия, 26 см</t>
+          <t>Сковорода глубокая FILIGRANA EDDA FG26EDD01DF из кованого алюминия, 26 см б/у</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -4647,7 +4647,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Сковорода из литого алюминия, 26 см MAUNFELD GRETA MF26GRTT01FP (Россия)</t>
+          <t>Сковорода из литого алюминия, 26 см MAUNFELD GRETA MF26GRTT01FP б/у</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -4663,7 +4663,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Сковорода из литого алюминия, 24 см MAUNFELD GRETA MF24GRTT01FP (РОССИЯ)</t>
+          <t>Сковорода из литого алюминия, 24 см MAUNFELD GRETA MF24GRTT01FP б/у</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -4679,7 +4679,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Сковорода блинная MAUNFELD HELGA МСP24FA05FS из кованого алюминия, 24 см (Китай)</t>
+          <t>Сковорода блинная MAUNFELD HELGA МСP24FA05FS из кованого алюминия, 24 см б/у</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -4695,7 +4695,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD HELGA MFP26FA05FS из кованого алюминия, 26 см (Китай)</t>
+          <t>Сковорода MAUNFELD HELGA MFP26FA05FS из кованого алюминия, 26 см б/у</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -4711,7 +4711,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Глубокая сковорода MAUNFELD FRIDA MDP24FA02DG из кованого алюминия, 24 см (Китай)</t>
+          <t>Глубокая сковорода MAUNFELD FRIDA MDP24FA02DG из кованого алюминия, 24 см б/у</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -4727,7 +4727,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Сковорода-гриль MAUNFELD DEVON MGP27CE16R из эмалированного чугуна, 27х27 см (Китай)</t>
+          <t>Сковорода-гриль MAUNFELD DEVON MGP27CE16R из эмалированного чугуна, 27х27 см б/у</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -4743,7 +4743,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Сковорода из литого алюминия, 28 см MAUNFELD ALVA MF28LV01FP (Россия)</t>
+          <t>Сковорода из литого алюминия, 28 см MAUNFELD ALVA MF28LV01FP б/у</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -4759,7 +4759,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD HELGA MFP28FA05FS из кованого алюминия, 28 см (Китай)</t>
+          <t>Сковорода MAUNFELD HELGA MFP28FA05FS из кованого алюминия, 28 см б/у</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -4775,7 +4775,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Глубокая сковорода MAUNFELD MARTA MDP28FA06CL из кованого алюминия, 28 см (Китай)</t>
+          <t>Глубокая сковорода MAUNFELD MARTA MDP28FA06CL из кованого алюминия, 28 см б/у</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -4791,7 +4791,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Глубокая сковорода MAUNFELD FRIDA MDP28FA02DG из кованого алюминия, 28 см (Китай)</t>
+          <t>Глубокая сковорода MAUNFELD FRIDA MDP28FA02DG из кованого алюминия, 28 см б/у</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -4807,7 +4807,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD FRIDA MFP24FA02DG из кованого алюминия, 24 см (Китай)</t>
+          <t>Сковорода MAUNFELD FRIDA MFP24FA02DG из кованого алюминия, 24 см б/у</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -4823,7 +4823,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Сковорода блинная MAUNFELD FRIDA MCP24FA02DG из кованого алюминия, 24 см (Китай)</t>
+          <t>Сковорода блинная MAUNFELD FRIDA MCP24FA02DG из кованого алюминия, 24 см б/у</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -4839,7 +4839,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Сковорода блинная из литого алюминия, 22 см MAUNFELD ALVA MF22LV01PP (РОССИЯ)</t>
+          <t>Сковорода блинная из литого алюминия, 22 см MAUNFELD ALVA MF22LV01PP б/у</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -4855,7 +4855,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Сковорода глубокая FILIGRANA CARITA FG26CRT01DP из кованого алюминия, 26 см</t>
+          <t>Сковорода глубокая FILIGRANA CARITA FG26CRT01DP из кованого алюминия, 26 см б/у</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -4871,7 +4871,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Сковорода MAUNFELD FRIDA MFP26FA02DG из кованого алюминия, 26 см (Китай)</t>
+          <t>Сковорода MAUNFELD FRIDA MFP26FA02DG из кованого алюминия, 26 см б/у</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -4887,7 +4887,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Сковорода-гриль MAUNFELD HOWARD MGP28LC15 из облегченного чугуна, 28х28 см (Китай)</t>
+          <t>Сковорода-гриль MAUNFELD HOWARD MGP28LC15 из облегченного чугуна, 28х28 см б/у</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -4903,7 +4903,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Сковорода блинная MAUNFELD GALAXITE MF22GLX01PP из литого алюминия, 22 см (Россия)</t>
+          <t>Сковорода блинная MAUNFELD GALAXITE MF22GLX01PP из литого алюминия, 22 см б/у</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -4919,7 +4919,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE10TGW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE10TGW б/у</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -4935,7 +4935,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Миксер MAUNFELD MF-321R (Китай)</t>
+          <t>Миксер MAUNFELD MF-321R б/у</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -4951,7 +4951,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Чайник MAUNFELD MFK-631GR (Китай)</t>
+          <t>Чайник MAUNFELD MFK-631GR б/у</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -4967,7 +4967,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFB10GW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFB10GW б/у</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -4983,7 +4983,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Проточный электрический водонагреватель MAUNFELD MWH35IS (Китай)</t>
+          <t>Проточный электрический водонагреватель MAUNFELD MWH35IS б/у</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -4999,7 +4999,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Кофемолка MAUNFELD MF-521S (Китай)</t>
+          <t>Кофемолка MAUNFELD MF-521S б/у</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -5015,7 +5015,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821BK (Китай)</t>
+          <t>Тостер MAUNFELD MF-821BK б/у</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -5031,7 +5031,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821WH (Китай)</t>
+          <t>Тостер MAUNFELD MF-821WH б/у</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -5047,7 +5047,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Миксер MAUNFELD MF-331GR (Китай)</t>
+          <t>Миксер MAUNFELD MF-331GR б/у</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -5063,7 +5063,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Тостер MAUNFELD MF-821CH (Китай)</t>
+          <t>Тостер MAUNFELD MF-821CH б/у</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -5079,7 +5079,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Power 60 белый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Power 60 белый б/у</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -5095,7 +5095,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Crosby Power 60 черный (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Crosby Power 60 черный б/у</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -5111,7 +5111,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Винный шкаф MAUNFELD MBWC-56D17 (Китай)</t>
+          <t>Винный шкаф MAUNFELD MBWC-56D17 б/у</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -5127,7 +5127,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Проточный электрический водонагреватель MAUNFELD MWH35IT (Китай)</t>
+          <t>Проточный электрический водонагреватель MAUNFELD MWH35IT б/у</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -5143,7 +5143,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD Tower C 60 белый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD Tower C 60 белый б/у</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -5159,7 +5159,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Кухонная вытяжка MAUNFELD MZR Cool 60 белый (Польша)</t>
+          <t>Кухонная вытяжка MAUNFELD MZR Cool 60 белый б/у</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -5175,7 +5175,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFS12W (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFS12W б/у</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -5191,7 +5191,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX12TW (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX12TW б/у</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -5207,7 +5207,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX12TBG (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX12TBG б/у</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -5223,7 +5223,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX12W (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX12W б/у</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -5239,7 +5239,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD EOEC.586B2 (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD EOEC.586B2 б/у</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -5255,7 +5255,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD EOEC.566TB Х</t>
+          <t>Шкаф духовой электрический MAUNFELD EOEC.566TB Х б/у</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -5271,7 +5271,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Сковорода вок MAUNFELD ELLA MF26EL01WF из литого алюминия, 26 см (Россия)</t>
+          <t>Сковорода вок MAUNFELD ELLA MF26EL01WF из литого алюминия, 26 см б/у</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -5287,7 +5287,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Винный шкаф MAUNFELD MFWC-50D16 (Китай)</t>
+          <t>Винный шкаф MAUNFELD MFWC-50D16 б/у</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -5303,7 +5303,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Кухонный комбайн MAUNFELD MF-421S PRO (Китай)</t>
+          <t>Кухонный комбайн MAUNFELD MF-421S PRO б/у</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -5319,7 +5319,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AMCO458S (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AMCO458S б/у</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -5335,7 +5335,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический с паром MAUNFELD MEOR7216STW (Китай)</t>
+          <t>Шкаф духовой электрический с паром MAUNFELD MEOR7216STW б/у</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -5351,7 +5351,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD AMCO537GB (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD AMCO537GB б/у</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -5367,7 +5367,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Шкаф духовой электрический MAUNFELD EOEC.586W (Китай)</t>
+          <t>Шкаф духовой электрический MAUNFELD EOEC.586W б/у</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -5383,7 +5383,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFB12GB (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFB12GB б/у</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -5399,7 +5399,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFE12TGGR (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFE12TGGR б/у</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -5415,7 +5415,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFS10W (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFS10W б/у</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -5431,7 +5431,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFB10GBG (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFB10GBG б/у</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -5447,7 +5447,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор  MAUNFELD MFB08GBG (Китай)</t>
+          <t>Вытяжной вентилятор  MAUNFELD MFB08GBG б/у</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -5463,7 +5463,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Вытяжной вентилятор MAUNFELD MFX12TS (Китай)</t>
+          <t>Вытяжной вентилятор MAUNFELD MFX12TS б/у</t>
         </is>
       </c>
       <c r="B315" t="n">
